--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.42568093385732</v>
+        <v>10.79417315175182</v>
       </c>
       <c r="D2" t="n">
-        <v>65.44340759996929</v>
+        <v>10.63455373499501</v>
       </c>
       <c r="E2" t="n">
-        <v>18.28817846757484</v>
+        <v>2.971829000980912</v>
       </c>
       <c r="F2" t="n">
-        <v>20.80096714258112</v>
+        <v>3.380157160669433</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.21065043350126</v>
+        <v>5.396730695443956</v>
       </c>
       <c r="D3" t="n">
-        <v>29.0342836437818</v>
+        <v>4.718071092114543</v>
       </c>
       <c r="E3" t="n">
-        <v>18.28817846757484</v>
+        <v>2.971829000980912</v>
       </c>
       <c r="F3" t="n">
-        <v>20.80096714258112</v>
+        <v>3.380157160669433</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.88462045216065</v>
+        <v>3.068750823476106</v>
       </c>
       <c r="D4" t="n">
-        <v>12.18035759372897</v>
+        <v>1.979308108980958</v>
       </c>
       <c r="E4" t="n">
-        <v>18.28817846757484</v>
+        <v>2.971829000980912</v>
       </c>
       <c r="F4" t="n">
-        <v>20.80096714258112</v>
+        <v>3.380157160669433</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.56818101314475</v>
+        <v>8.704829414636022</v>
       </c>
       <c r="D5" t="n">
-        <v>53.75562754615553</v>
+        <v>8.735289476250275</v>
       </c>
       <c r="E5" t="n">
-        <v>18.28817846757484</v>
+        <v>2.971829000980912</v>
       </c>
       <c r="F5" t="n">
-        <v>20.80096714258112</v>
+        <v>3.380157160669433</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
